--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:22</t>
+    <t xml:space="preserve">2026-09-09 23:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:18</t>
+    <t xml:space="preserve">2026-09-17 14:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_valparaiso.xlsx
@@ -87,12 +87,12 @@
     <t xml:space="preserve">Casablanca</t>
   </si>
   <si>
+    <t xml:space="preserve">Calera</t>
+  </si>
+  <si>
     <t xml:space="preserve">Algarrobo</t>
   </si>
   <si>
-    <t xml:space="preserve">Calera</t>
-  </si>
-  <si>
     <t xml:space="preserve">Zapallar</t>
   </si>
   <si>
@@ -138,12 +138,12 @@
     <t xml:space="preserve">Cartagena</t>
   </si>
   <si>
+    <t xml:space="preserve">La Ligua</t>
+  </si>
+  <si>
     <t xml:space="preserve">El Quisco</t>
   </si>
   <si>
-    <t xml:space="preserve">La Ligua</t>
-  </si>
-  <si>
     <t xml:space="preserve">Olmué</t>
   </si>
   <si>
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:13</t>
+    <t xml:space="preserve">2026-09-23 12:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -875,7 +875,7 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>5602</v>
+        <v>5502</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2022</v>
@@ -892,7 +892,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>5502</v>
+        <v>5602</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2022</v>
@@ -1181,7 +1181,7 @@
         <v>40</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>5604</v>
+        <v>5401</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>2022</v>
@@ -1198,7 +1198,7 @@
         <v>41</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>5401</v>
+        <v>5604</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>2022</v>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:42</t>
+    <t xml:space="preserve">2026-10-02 14:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:56</t>
+    <t xml:space="preserve">2026-10-04 09:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:13</t>
+    <t xml:space="preserve">2026-10-05 11:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
